--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/biobio.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/biobio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Curanilahue - Salud</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2466,7 +2466,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2410-2654-CM25</t>
+          <t>2410-2656-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>ENILDA TERESA FIGUEROA MELLADO</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>6.189.318-0</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>12821.9</v>
+        <v>10011.5</v>
       </c>
     </row>
     <row r="35">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2588,7 +2588,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2410-2656-CM25</t>
+          <t>2410-2654-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>ENILDA TERESA FIGUEROA MELLADO</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>6.189.318-0</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>10011.5</v>
+        <v>12821.9</v>
       </c>
     </row>
     <row r="37">
@@ -2832,7 +2832,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1079576-107-CM26</t>
+          <t>1456839-6-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>61.981.420-7</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VIII ZONA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS COPIHUES</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>14341.16</v>
+        <v>6764.22</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1456840-15-CM26</t>
+          <t>1389183-36-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.981.460-6</t>
+          <t>61.981.100-3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL RELONCAVÍ</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>ENILDA TERESA FIGUEROA MELLADO</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
+          <t>6.189.318-0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>12814.34</v>
+        <v>48333.5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4034-206-CM26</t>
+          <t>1079576-107-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2964,27 +2964,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.160.501-9</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cañete - Educación</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>16269.06</v>
+        <v>14341.16</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1426098-122-CM26</t>
+          <t>4034-206-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,22 +3030,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.160.501-9</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>19027.83</v>
+        <v>16269.06</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4494-279-CM26</t>
+          <t>1426098-122-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,22 +3091,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>11649.04</v>
+        <v>19027.83</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2421-599-CM26</t>
+          <t>4494-279-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,22 +3152,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.256.900-8</t>
+          <t>69.150.500-6</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dirección de Administración de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>12513.33</v>
+        <v>11649.04</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1079650-29-SE26</t>
+          <t>2421-599-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.607.100-9</t>
+          <t>69.256.900-8</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,32 +3238,28 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>BLUEMEDICAL SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.116.604-2</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>12377.65</v>
+        <v>12513.33</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1057432-197-CM26</t>
+          <t>1079650-29-SE26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3273,12 +3269,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3303,28 +3299,32 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>BLUEMEDICAL SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+          <t>76.116.604-2</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>10117.15</v>
+        <v>12377.65</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1057934-10-CM26</t>
+          <t>1057432-197-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3344,17 +3344,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.607.202-1</t>
+          <t>61.607.100-9</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE TALCAHUANO HOSPITAL</t>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3379,13 +3379,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>22179.22</v>
+        <v>10117.15</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4081-202-CM26</t>
+          <t>1057934-10-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3405,17 +3405,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.151.001-8</t>
+          <t>61.607.202-1</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabrero</t>
+          <t>SERVICIO DE SALUD DE TALCAHUANO HOSPITAL</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3425,12 +3425,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3440,13 +3440,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>14611.23</v>
+        <v>22179.22</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2760-71-CM26</t>
+          <t>4081-202-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3471,12 +3471,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.151.200-2</t>
+          <t>69.151.001-8</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3501,13 +3501,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>8444.290000000001</v>
+        <v>14611.23</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1079650-57-CM26</t>
+          <t>2760-71-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3532,12 +3532,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.607.100-9</t>
+          <t>69.151.200-2</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>92.999.000-5</t>
+          <t>76.058.118-6</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3562,13 +3562,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>9929.620000000001</v>
+        <v>8444.290000000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2178-186-CM26</t>
+          <t>1079650-57-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3583,22 +3583,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.607.100-9</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>92.999.000-5</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3623,13 +3623,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>21833.41</v>
+        <v>9929.620000000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>654-246-CM26</t>
+          <t>2178-186-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3639,27 +3639,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.820.004-3</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3669,12 +3669,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3684,13 +3684,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>11835.75</v>
+        <v>21833.41</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1057822-13-CM26</t>
+          <t>654-246-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.607.100-9</t>
+          <t>61.820.004-3</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CONCEPCION</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3745,13 +3745,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>17534.53</v>
+        <v>11835.75</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2704-1424-CM26</t>
+          <t>1057822-13-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>61.607.100-9</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3806,13 +3806,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>10348.34</v>
+        <v>17534.53</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>654-256-CM26</t>
+          <t>2704-1424-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.820.004-3</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3852,12 +3852,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
+          <t>76.028.554-4</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3867,13 +3867,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>22141.2</v>
+        <v>10348.34</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1777-67-CM26</t>
+          <t>654-256-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>60.804.012-9</t>
+          <t>61.820.004-3</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE TALCAHUANO</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3913,12 +3913,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.058.118-6</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3928,13 +3928,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>11082.73</v>
+        <v>22141.2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>654-278-CM26</t>
+          <t>1777-67-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.820.004-3</t>
+          <t>60.804.012-9</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3989,13 +3989,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>17071.99</v>
+        <v>11082.73</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1389183-367-CM26</t>
+          <t>654-278-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4020,12 +4020,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.981.100-3</t>
+          <t>61.820.004-3</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4035,12 +4035,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4050,13 +4050,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>59729.87</v>
+        <v>17071.99</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2704-1693-CM26</t>
+          <t>1389183-367-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4071,22 +4071,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>61.981.100-3</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4111,13 +4111,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>6464.65</v>
+        <v>59729.87</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4083-414-CM26</t>
+          <t>2704-1693-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.151.002-6</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4172,13 +4172,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>13074.04</v>
+        <v>6464.65</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1057934-17-CM26</t>
+          <t>4083-414-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4193,22 +4193,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.607.202-1</t>
+          <t>69.151.002-6</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE TALCAHUANO HOSPITAL</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.619.564-2</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4233,7 +4233,617 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
+        <v>13074.04</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1057934-17-CM26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>61.607.202-1</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DE TALCAHUANO HOSPITAL</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
         <v>10291.91</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>707422-152-CM26</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>FAST OFFICE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>77.205.938-8</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>9601.82</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1079650-102-CM26</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>61.607.100-9</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>92.999.000-5</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>25782.37</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1079650-119-CM26</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>61.607.100-9</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>10365.18</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>1208129-458-CM26</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>62.000.890-7</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>LOYDA EUGENIA HENRÍQUEZ ORELLANA</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>11.216.890-7</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>29216.36</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>4081-303-CM26</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>69.151.001-8</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>LOYDA EUGENIA HENRÍQUEZ ORELLANA</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>11.216.890-7</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>13249.78</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>1057822-102-CM26</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>61.607.100-9</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>92.999.000-5</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>24243.55</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1057822-113-CM26</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>61.607.100-9</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>92.999.000-5</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>11377.04</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>1389183-606-CM26</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>61.981.100-3</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>24468.88</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>1057822-121-CM26</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>61.607.100-9</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>6909.92</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/biobio.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/biobio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>76.855.435-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +749,11 @@
           <t>76.058.118-6</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +944,11 @@
           <t>76.559.762-5</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -941,7 +961,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2178-117-CM25</t>
+          <t>1079650-11-SE25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,27 +971,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.607.100-9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,28 +1001,32 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>ALQUEZAR SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>77.714.556-8</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>16405.53</v>
+        <v>8844.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4375-1529-CM25</t>
+          <t>2178-117-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1041,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1051,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.602.189-3</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>HOSPITAL GUILLERMO GRANT BENAVENTE DE CO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,28 +1066,32 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>suria ltda</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.827.520-1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>76.058.118-6</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>6179.38</v>
+        <v>16405.53</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1426098-160-CM25</t>
+          <t>4375-1529-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1101,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1116,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.602.189-3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>HOSPITAL GUILLERMO GRANT BENAVENTE DE CO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1131,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>suria ltda</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>77.827.520-1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1146,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>23292.34</v>
+        <v>6179.38</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2421-3979-CM25</t>
+          <t>1426098-160-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1167,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1177,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.256.900-8</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,28 +1192,32 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>FRANCISCO ANTONIO PALACIOS MUÑOZ</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>14.164.209-K</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>7126.39</v>
+        <v>23292.34</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4229-79-CM25</t>
+          <t>2421-3979-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1227,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1242,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>69.256.900-8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,28 +1257,32 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>FRANCISCO ANTONIO PALACIOS MUÑOZ</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>14.164.209-K</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>15430.84</v>
+        <v>7126.39</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2421-4025-CM25</t>
+          <t>2421-3990-SE25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1292,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1286,28 +1322,32 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CLINICON SPA</t>
+          <t>FRANCISCO ANTONIO PALACIOS MUÑOZ</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.070.635-1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>14.164.209-K</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>10291.28</v>
+        <v>1267.07</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1550-20-CM25</t>
+          <t>4229-79-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1362,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1372,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60.803.000-k</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,28 +1387,32 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>25027.85</v>
+        <v>15430.84</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2888-39-CM25</t>
+          <t>2421-4025-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1427,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1437,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>69.256.900-8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1452,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>CLINICON SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.070.635-1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1467,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>7195.48</v>
+        <v>10291.28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2410-383-CM25</t>
+          <t>1550-20-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,7 +1488,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1498,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>60.803.000-k</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,28 +1513,32 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>92.999.000-5</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>22197.36</v>
+        <v>25027.85</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4083-435-CM25</t>
+          <t>2888-39-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,27 +1548,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.151.002-6</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,28 +1578,32 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Inversiones Cuatro Rios S.A.</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.094.593-5</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>11999.41</v>
+        <v>7195.48</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2704-1496-CM25</t>
+          <t>2410-383-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1613,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1628,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1643,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>92.999.000-5</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1658,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>14609.82</v>
+        <v>22197.36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2360-668-CM25</t>
+          <t>4083-435-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,27 +1674,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.150.800-5</t>
+          <t>69.151.002-6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1704,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>Inversiones Cuatro Rios S.A.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.094.593-5</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1719,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>9014.040000000001</v>
+        <v>11999.41</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1057931-52-CM25</t>
+          <t>2421-4235-SE25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1735,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1750,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>69.256.900-8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1721,20 +1773,24 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>10404.71</v>
+        <v>15557.05</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3076-329-CM25</t>
+          <t>2704-1496-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1800,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1815,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.102.022-8</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,28 +1830,32 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>13824.03</v>
+        <v>14609.82</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1057931-84-CM25</t>
+          <t>2360-668-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,7 +1870,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1880,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>69.150.800-5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1843,20 +1903,24 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>11047.77</v>
+        <v>9014.040000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2410-558-CM25</t>
+          <t>1057931-52-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1930,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1945,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,28 +1960,32 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>7501.23</v>
+        <v>10404.71</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1057931-110-CM25</t>
+          <t>3076-329-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,12 +1995,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +2010,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>61.102.022-8</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,28 +2025,32 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>9022.9</v>
+        <v>13824.03</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1079576-4068-CM25</t>
+          <t>1057931-84-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,12 +2060,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2075,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2026,50 +2098,54 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>18734.57</v>
+        <v>11047.77</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4858-1013-CM25</t>
+          <t>2410-558-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.160.700-3</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIRUA</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,43 +2155,47 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>9892.59</v>
+        <v>7501.23</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>654-403-CM25</t>
+          <t>1057931-110-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2205,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.820.004-3</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,43 +2220,47 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>24201.95</v>
+        <v>9022.9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>654-400-CM25</t>
+          <t>1079576-4068-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2270,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.820.004-3</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,53 +2285,57 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>ENILDA TERESA FIGUEROA MELLADO</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>6.189.318-0</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>19556.67</v>
+        <v>18734.57</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2409-1784-CM25</t>
+          <t>2410-675-SE25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.170.101-8</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2262,28 +2350,32 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t xml:space="preserve">Rescatelife limitada </t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>76.217.441-3</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>10752.28</v>
+        <v>5850.42</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1208129-730-CM25</t>
+          <t>4858-1013-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,22 +2390,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>69.160.700-3</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>I MUNICIPALIDAD DE TIRUA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,28 +2415,32 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>12194.06</v>
+        <v>9892.59</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4238-396-CM25</t>
+          <t>654-400-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,7 +2455,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2465,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.160.202-8</t>
+          <t>61.820.004-3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2480,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>ENILDA TERESA FIGUEROA MELLADO</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>6.189.318-0</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2495,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>13846.53</v>
+        <v>19556.67</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2178-421-CM25</t>
+          <t>654-403-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,12 +2511,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2526,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.820.004-3</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,28 +2541,32 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>13194.41</v>
+        <v>24201.95</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2410-2656-CM25</t>
+          <t>2409-1784-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,22 +2576,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2506,28 +2606,32 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>10011.5</v>
+        <v>10752.28</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2410-2655-CM25</t>
+          <t>1208129-730-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2537,12 +2641,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,12 +2656,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,28 +2671,32 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>6366.61</v>
+        <v>12194.06</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2410-2654-CM25</t>
+          <t>4238-396-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2598,12 +2706,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,12 +2721,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>69.160.202-8</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,28 +2736,32 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>ENILDA TERESA FIGUEROA MELLADO</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>6.189.318-0</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>12821.9</v>
+        <v>13846.53</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1563-93-CM25</t>
+          <t>2178-421-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,7 +2776,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,12 +2786,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,28 +2801,32 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>9510.889999999999</v>
+        <v>13194.41</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2178-432-CM25</t>
+          <t>2410-2654-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,7 +2841,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,12 +2851,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2866,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>ENILDA TERESA FIGUEROA MELLADO</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>6.189.318-0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2881,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>7755.95</v>
+        <v>12821.9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4375-188-CM26</t>
+          <t>2410-2655-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,12 +2897,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,12 +2912,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.602.189-3</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>HOSPITAL GUILLERMO GRANT BENAVENTE DE CO</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,28 +2927,32 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>suria ltda</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>77.827.520-1</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>12131.25</v>
+        <v>6366.61</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1456839-6-CM26</t>
+          <t>2410-2656-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,12 +2962,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,12 +2977,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.981.420-7</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS COPIHUES</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,28 +2992,32 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>6764.22</v>
+        <v>10011.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1389183-36-CM26</t>
+          <t>1563-93-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2903,12 +3027,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +3042,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.981.100-3</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +3057,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>ENILDA TERESA FIGUEROA MELLADO</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>6.189.318-0</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +3072,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>48333.5</v>
+        <v>9510.889999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1079576-107-CM26</t>
+          <t>2178-432-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2964,12 +3088,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,12 +3103,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,28 +3118,32 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>14341.16</v>
+        <v>7755.95</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4034-206-CM26</t>
+          <t>4375-188-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3025,27 +3153,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>69.160.501-9</t>
+          <t>61.602.189-3</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANETE</t>
+          <t>HOSPITAL GUILLERMO GRANT BENAVENTE DE CO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3183,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>suria ltda</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.827.520-1</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3198,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>16269.06</v>
+        <v>12131.25</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1426098-122-CM26</t>
+          <t>1456839-6-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3086,12 +3214,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3229,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.981.420-7</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS COPIHUES</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,28 +3244,32 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>19027.83</v>
+        <v>6764.22</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4494-279-CM26</t>
+          <t>1389183-36-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3147,27 +3279,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>61.981.100-3</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3309,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>ENILDA TERESA FIGUEROA MELLADO</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>6.189.318-0</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3324,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>11649.04</v>
+        <v>48333.5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2421-599-CM26</t>
+          <t>1079576-107-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3208,12 +3340,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3223,12 +3355,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.256.900-8</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,12 +3370,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3385,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>12513.33</v>
+        <v>14341.16</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1079650-29-SE26</t>
+          <t>4034-206-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,7 +3406,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,12 +3416,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.607.100-9</t>
+          <t>69.160.501-9</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,12 +3431,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>BLUEMEDICAL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.116.604-2</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3318,13 +3450,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>12377.65</v>
+        <v>16269.06</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1057432-197-CM26</t>
+          <t>1426098-122-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3334,27 +3466,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.607.100-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CONCEPCION</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3372,20 +3504,24 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>10117.15</v>
+        <v>19027.83</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1057934-10-CM26</t>
+          <t>4494-279-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3395,27 +3531,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.607.202-1</t>
+          <t>69.150.500-6</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE TALCAHUANO HOSPITAL</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3425,28 +3561,32 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>22179.22</v>
+        <v>11649.04</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4081-202-CM26</t>
+          <t>2421-599-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3456,27 +3596,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.151.001-8</t>
+          <t>69.256.900-8</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3486,28 +3626,32 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>14611.23</v>
+        <v>12513.33</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2760-71-CM26</t>
+          <t>1079650-29-SE26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3517,12 +3661,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3532,12 +3676,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.151.200-2</t>
+          <t>61.607.100-9</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL</t>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3547,28 +3691,32 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>BLUEMEDICAL SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+          <t>76.116.604-2</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>8444.290000000001</v>
+        <v>12377.65</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1079650-57-CM26</t>
+          <t>1057432-197-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3583,7 +3731,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3608,28 +3756,32 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>92.999.000-5</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>9929.620000000001</v>
+        <v>10117.15</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2178-186-CM26</t>
+          <t>1057934-10-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3644,7 +3796,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3654,12 +3806,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.607.202-1</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO DE SALUD DE TALCAHUANO HOSPITAL</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3669,28 +3821,32 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>21833.41</v>
+        <v>22179.22</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>654-246-CM26</t>
+          <t>4081-202-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3700,12 +3856,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3715,12 +3871,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.820.004-3</t>
+          <t>69.151.001-8</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3730,28 +3886,32 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>11835.75</v>
+        <v>14611.23</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1057822-13-CM26</t>
+          <t>2760-71-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3761,12 +3921,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3776,12 +3936,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.607.100-9</t>
+          <t>69.151.200-2</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3791,28 +3951,32 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
+          <t>76.058.118-6</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>17534.53</v>
+        <v>8444.290000000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2704-1424-CM26</t>
+          <t>1079650-57-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3822,12 +3986,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3837,12 +4001,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>61.607.100-9</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3852,12 +4016,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
+          <t>92.999.000-5</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3867,13 +4031,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>10348.34</v>
+        <v>9929.620000000001</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>654-256-CM26</t>
+          <t>2178-186-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3883,27 +4047,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.820.004-3</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3913,28 +4077,32 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>22141.2</v>
+        <v>21833.41</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1777-67-CM26</t>
+          <t>654-246-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3949,7 +4117,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3959,12 +4127,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>60.804.012-9</t>
+          <t>61.820.004-3</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3974,28 +4142,32 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>11082.73</v>
+        <v>11835.75</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>654-278-CM26</t>
+          <t>1057822-13-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4005,12 +4177,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4020,12 +4192,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.820.004-3</t>
+          <t>61.607.100-9</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4043,20 +4215,24 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>17071.99</v>
+        <v>17534.53</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1389183-367-CM26</t>
+          <t>2704-1424-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4066,27 +4242,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.981.100-3</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4096,12 +4272,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>76.028.554-4</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4111,13 +4287,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>59729.87</v>
+        <v>10348.34</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2704-1693-CM26</t>
+          <t>654-256-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4127,12 +4303,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4142,12 +4318,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>61.820.004-3</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4157,28 +4333,32 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
+          <t>76.058.118-6</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>6464.65</v>
+        <v>22141.2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>4083-414-CM26</t>
+          <t>1777-67-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4188,12 +4368,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4203,12 +4383,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.151.002-6</t>
+          <t>60.804.012-9</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4218,28 +4398,32 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>13074.04</v>
+        <v>11082.73</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1057934-17-CM26</t>
+          <t>654-278-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4254,22 +4438,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.607.202-1</t>
+          <t>61.820.004-3</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE TALCAHUANO HOSPITAL</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4279,28 +4463,32 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>10291.91</v>
+        <v>17071.99</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>707422-152-CM26</t>
+          <t>1389183-367-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4310,27 +4498,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.981.100-3</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4340,12 +4528,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>FAST OFFICE LIMITADA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>77.205.938-8</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4355,13 +4543,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>9601.82</v>
+        <v>59729.87</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1079650-102-CM26</t>
+          <t>2704-1693-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4371,12 +4559,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4386,12 +4574,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.607.100-9</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CONCEPCION</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4401,28 +4589,32 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>92.999.000-5</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>25782.37</v>
+        <v>6464.65</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1079650-119-CM26</t>
+          <t>4083-414-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4432,12 +4624,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4447,12 +4639,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.607.100-9</t>
+          <t>69.151.002-6</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4462,28 +4654,32 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
+          <t>77.619.564-2</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>10365.18</v>
+        <v>13074.04</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1208129-458-CM26</t>
+          <t>1057934-17-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4493,27 +4689,27 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.607.202-1</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>SERVICIO DE SALUD DE TALCAHUANO HOSPITAL</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4523,28 +4719,32 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>LOYDA EUGENIA HENRÍQUEZ ORELLANA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>11.216.890-7</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>29216.36</v>
+        <v>10291.91</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>4081-303-CM26</t>
+          <t>707422-152-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4559,7 +4759,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4569,12 +4769,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.151.001-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4584,12 +4784,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>LOYDA EUGENIA HENRÍQUEZ ORELLANA</t>
+          <t>FAST OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>11.216.890-7</t>
+          <t>77.205.938-8</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4599,13 +4799,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>13249.78</v>
+        <v>9601.82</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1057822-102-CM26</t>
+          <t>1079650-102-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4620,7 +4820,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4660,13 +4860,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>24243.55</v>
+        <v>25782.37</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1057822-113-CM26</t>
+          <t>1079650-119-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4681,7 +4881,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4706,28 +4906,32 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>92.999.000-5</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>11377.04</v>
+        <v>10365.18</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1389183-606-CM26</t>
+          <t>1208129-458-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4742,7 +4946,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4752,12 +4956,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.981.100-3</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4767,12 +4971,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>LOYDA EUGENIA HENRÍQUEZ ORELLANA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>11.216.890-7</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4782,13 +4986,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>24468.88</v>
+        <v>29216.36</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1057822-121-CM26</t>
+          <t>4081-303-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4803,7 +5007,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4813,12 +5017,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.607.100-9</t>
+          <t>69.151.001-8</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4828,12 +5032,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>LOYDA EUGENIA HENRÍQUEZ ORELLANA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>11.216.890-7</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4843,6 +5047,254 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
+        <v>13249.78</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>1057822-102-CM26</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>61.607.100-9</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>92.999.000-5</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>24243.55</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1057822-113-CM26</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>61.607.100-9</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>92.999.000-5</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>11377.04</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1389183-606-CM26</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>61.981.100-3</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>24468.88</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>1057822-121-CM26</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>61.607.100-9</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="n">
         <v>6909.92</v>
       </c>
     </row>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/biobio.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/biobio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:M78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -766,7 +766,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1057931-2-CM25</t>
+          <t>1057931-1-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1057931-1-CM25</t>
+          <t>1057931-2-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1217,7 +1217,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2421-3979-CM25</t>
+          <t>2421-3990-SE25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1276,13 +1276,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>7126.39</v>
+        <v>1267.07</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2421-3990-SE25</t>
+          <t>2421-3979-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1267.07</v>
+        <v>7126.39</v>
       </c>
     </row>
     <row r="15">
@@ -2440,7 +2440,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>654-400-CM25</t>
+          <t>654-403-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2480,28 +2480,32 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>ENILDA TERESA FIGUEROA MELLADO</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>6.189.318-0</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>19556.67</v>
+        <v>24201.95</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>654-403-CM25</t>
+          <t>654-400-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2541,26 +2545,22 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>ENILDA TERESA FIGUEROA MELLADO</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>6.189.318-0</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>24201.95</v>
+        <v>19556.67</v>
       </c>
     </row>
     <row r="34">
@@ -2826,7 +2826,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2410-2654-CM25</t>
+          <t>2410-2656-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2866,22 +2866,26 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>ENILDA TERESA FIGUEROA MELLADO</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>6.189.318-0</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>12821.9</v>
+        <v>10011.5</v>
       </c>
     </row>
     <row r="39">
@@ -2952,7 +2956,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2410-2656-CM25</t>
+          <t>2410-2654-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2992,26 +2996,22 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>ENILDA TERESA FIGUEROA MELLADO</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>6.189.318-0</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>10011.5</v>
+        <v>12821.9</v>
       </c>
     </row>
     <row r="41">
@@ -5053,7 +5053,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1057822-102-CM26</t>
+          <t>1057822-113-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5108,13 +5108,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>24243.55</v>
+        <v>11377.04</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1057822-113-CM26</t>
+          <t>1057822-102-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>11377.04</v>
+        <v>24243.55</v>
       </c>
     </row>
     <row r="75">
@@ -5296,6 +5296,132 @@
       </c>
       <c r="M76" s="2" t="n">
         <v>6909.92</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>3567-551-CM26</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>69.150.700-9</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE FLORIDA</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>STATUS SPA</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>12076.24</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1079650-169-CM26</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>61.607.100-9</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>92.999.000-5</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>11308.33</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/biobio.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/biobio.xlsx
@@ -3736,7 +3736,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/biobio.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/biobio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5366,61 +5366,126 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>1417966-83-CM26</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>65.063.166-8</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>CORPORACIÓN DESARROLLA BIOBÍO</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>STATUS SPA</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>9972.780000000001</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
           <t>1079650-169-CM26</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>2239-4-LR25</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>61.607.100-9</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>SERVICIO DE SALUD CONCEPCION</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
         <is>
           <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>92.999.000-5</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="n">
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="n">
         <v>11308.33</v>
       </c>
     </row>
